--- a/outputs/AI_v_Student_results.xlsx
+++ b/outputs/AI_v_Student_results.xlsx
@@ -1133,13 +1133,13 @@
         <v>45</v>
       </c>
       <c r="B3" t="n">
-        <v>0.709999999999655</v>
+        <v>0.709999999999656</v>
       </c>
       <c r="C3" t="n">
         <v>0.66360832407841</v>
       </c>
       <c r="D3" t="n">
-        <v>0.752381112753435</v>
+        <v>0.752381112753436</v>
       </c>
     </row>
     <row r="5">
@@ -1280,13 +1280,13 @@
         <v>61</v>
       </c>
       <c r="B4" t="n">
-        <v>0.788819875776286</v>
+        <v>0.788819875776287</v>
       </c>
       <c r="C4" t="n">
-        <v>0.718971770081877</v>
+        <v>0.718971770081878</v>
       </c>
       <c r="D4" t="n">
-        <v>0.845049062875378</v>
+        <v>0.845049062875379</v>
       </c>
     </row>
     <row r="5">
@@ -1294,13 +1294,13 @@
         <v>45</v>
       </c>
       <c r="B5" t="n">
-        <v>0.709999999999655</v>
+        <v>0.709999999999656</v>
       </c>
       <c r="C5" t="n">
         <v>0.66360832407841</v>
       </c>
       <c r="D5" t="n">
-        <v>0.752381112753435</v>
+        <v>0.752381112753436</v>
       </c>
     </row>
     <row r="7">
@@ -1345,10 +1345,10 @@
         <v>0.136251766929717</v>
       </c>
       <c r="D9" t="n">
-        <v>4.76710557756657</v>
+        <v>4.76710557756656</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00000186891386661359</v>
+        <v>0.00000186891386661363</v>
       </c>
       <c r="F9" t="n">
         <v>1.91463414634127</v>
@@ -1357,7 +1357,7 @@
         <v>1.46591262696211</v>
       </c>
       <c r="H9" t="n">
-        <v>2.50071105665611</v>
+        <v>2.50071105665612</v>
       </c>
     </row>
     <row r="10">
@@ -1365,25 +1365,25 @@
         <v>62</v>
       </c>
       <c r="B10" t="n">
-        <v>0.668300003757806</v>
+        <v>0.668300003757812</v>
       </c>
       <c r="C10" t="n">
-        <v>0.23632666315873</v>
+        <v>0.236326663158731</v>
       </c>
       <c r="D10" t="n">
-        <v>2.82786544194947</v>
+        <v>2.82786544194948</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00468594980491761</v>
+        <v>0.00468594980491739</v>
       </c>
       <c r="F10" t="n">
-        <v>1.95091794679544</v>
+        <v>1.95091794679546</v>
       </c>
       <c r="G10" t="n">
-        <v>1.22765795834883</v>
+        <v>1.22765795834884</v>
       </c>
       <c r="H10" t="n">
-        <v>3.10027789845278</v>
+        <v>3.10027789845281</v>
       </c>
     </row>
     <row r="12">
@@ -1410,13 +1410,13 @@
         <v>66</v>
       </c>
       <c r="B14" t="n">
-        <v>8.33873779097223</v>
+        <v>8.33873779097229</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00388085505661369</v>
+        <v>0.00388085505661358</v>
       </c>
     </row>
   </sheetData>
@@ -1469,7 +1469,7 @@
         <v>0.644444444444435</v>
       </c>
       <c r="C3" t="n">
-        <v>0.540686888517164</v>
+        <v>0.540686888517165</v>
       </c>
       <c r="D3" t="n">
         <v>0.736199111571064</v>
@@ -1494,13 +1494,13 @@
         <v>70</v>
       </c>
       <c r="B5" t="n">
-        <v>0.740909090908515</v>
+        <v>0.740909090908516</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6789828599846</v>
+        <v>0.678982859984601</v>
       </c>
       <c r="D5" t="n">
-        <v>0.794504824101747</v>
+        <v>0.794504824101748</v>
       </c>
     </row>
     <row r="6">
@@ -1508,13 +1508,13 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.709999999999655</v>
+        <v>0.709999999999656</v>
       </c>
       <c r="C6" t="n">
         <v>0.66360832407841</v>
       </c>
       <c r="D6" t="n">
-        <v>0.752381112753435</v>
+        <v>0.752381112753436</v>
       </c>
     </row>
     <row r="8">
@@ -1553,25 +1553,25 @@
         <v>54</v>
       </c>
       <c r="B10" t="n">
-        <v>0.594707107746649</v>
+        <v>0.594707107746653</v>
       </c>
       <c r="C10" t="n">
         <v>0.220207565922281</v>
       </c>
       <c r="D10" t="n">
-        <v>2.70066609771502</v>
+        <v>2.70066609771503</v>
       </c>
       <c r="E10" t="n">
-        <v>0.006920077361676</v>
+        <v>0.00692007736167571</v>
       </c>
       <c r="F10" t="n">
-        <v>1.81249999999992</v>
+        <v>1.81249999999993</v>
       </c>
       <c r="G10" t="n">
         <v>1.17716406303235</v>
       </c>
       <c r="H10" t="n">
-        <v>2.79073780211845</v>
+        <v>2.79073780211846</v>
       </c>
     </row>
     <row r="11">
@@ -1579,22 +1579,22 @@
         <v>71</v>
       </c>
       <c r="B11" t="n">
-        <v>0.25259075263938</v>
+        <v>0.252590752639378</v>
       </c>
       <c r="C11" t="n">
-        <v>0.318435823686021</v>
+        <v>0.31843582368602</v>
       </c>
       <c r="D11" t="n">
-        <v>0.793223418507196</v>
+        <v>0.793223418507192</v>
       </c>
       <c r="E11" t="n">
-        <v>0.427647665668261</v>
+        <v>0.427647665668264</v>
       </c>
       <c r="F11" t="n">
         <v>1.28735632183762</v>
       </c>
       <c r="G11" t="n">
-        <v>0.689676940522787</v>
+        <v>0.689676940522786</v>
       </c>
       <c r="H11" t="n">
         <v>2.40298928672176</v>
@@ -1605,22 +1605,22 @@
         <v>72</v>
       </c>
       <c r="B12" t="n">
-        <v>0.455991825222564</v>
+        <v>0.455991825222565</v>
       </c>
       <c r="C12" t="n">
-        <v>0.268645046183894</v>
+        <v>0.268645046183893</v>
       </c>
       <c r="D12" t="n">
-        <v>1.6973766376858</v>
+        <v>1.69737663768581</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0896254765198322</v>
+        <v>0.0896254765198308</v>
       </c>
       <c r="F12" t="n">
         <v>1.57773744706128</v>
       </c>
       <c r="G12" t="n">
-        <v>0.931887863262772</v>
+        <v>0.931887863262774</v>
       </c>
       <c r="H12" t="n">
         <v>2.67119634238387</v>
@@ -1706,13 +1706,13 @@
         <v>75</v>
       </c>
       <c r="B3" t="n">
-        <v>0.799999999999969</v>
+        <v>0.799999999999967</v>
       </c>
       <c r="C3" t="n">
-        <v>0.459292094884389</v>
+        <v>0.459292094884388</v>
       </c>
       <c r="D3" t="n">
-        <v>0.949587166775102</v>
+        <v>0.949587166775101</v>
       </c>
     </row>
     <row r="4">
@@ -1720,10 +1720,10 @@
         <v>76</v>
       </c>
       <c r="B4" t="n">
-        <v>0.699999999999756</v>
+        <v>0.699999999999755</v>
       </c>
       <c r="C4" t="n">
-        <v>0.516601369295774</v>
+        <v>0.516601369295773</v>
       </c>
       <c r="D4" t="n">
         <v>0.835918220259369</v>
@@ -1734,13 +1734,13 @@
         <v>77</v>
       </c>
       <c r="B5" t="n">
-        <v>0.625000000000003</v>
+        <v>0.625</v>
       </c>
       <c r="C5" t="n">
-        <v>0.467720977181843</v>
+        <v>0.46772097718184</v>
       </c>
       <c r="D5" t="n">
-        <v>0.759683877585146</v>
+        <v>0.759683877585144</v>
       </c>
     </row>
     <row r="6">
@@ -1765,7 +1765,7 @@
         <v>0.766666666666272</v>
       </c>
       <c r="C7" t="n">
-        <v>0.585049009418909</v>
+        <v>0.585049009418908</v>
       </c>
       <c r="D7" t="n">
         <v>0.884487837107378</v>
@@ -1782,7 +1782,7 @@
         <v>0.636594775360551</v>
       </c>
       <c r="D8" t="n">
-        <v>0.76573109656423</v>
+        <v>0.765731096564229</v>
       </c>
     </row>
     <row r="9">
@@ -1790,13 +1790,13 @@
         <v>45</v>
       </c>
       <c r="B9" t="n">
-        <v>0.709999999999655</v>
+        <v>0.709999999999656</v>
       </c>
       <c r="C9" t="n">
         <v>0.66360832407841</v>
       </c>
       <c r="D9" t="n">
-        <v>0.752381112753435</v>
+        <v>0.752381112753436</v>
       </c>
     </row>
     <row r="11">
@@ -1835,25 +1835,25 @@
         <v>54</v>
       </c>
       <c r="B13" t="n">
-        <v>1.3862943611197</v>
+        <v>1.38629436111968</v>
       </c>
       <c r="C13" t="n">
-        <v>0.790569219544428</v>
+        <v>0.790569219544423</v>
       </c>
       <c r="D13" t="n">
         <v>1.75353950906229</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0795094439565111</v>
+        <v>0.0795094439565122</v>
       </c>
       <c r="F13" t="n">
-        <v>3.99999999999923</v>
+        <v>3.99999999999917</v>
       </c>
       <c r="G13" t="n">
-        <v>0.849427372041445</v>
+        <v>0.849427372041442</v>
       </c>
       <c r="H13" t="n">
-        <v>18.8362189948514</v>
+        <v>18.836218994851</v>
       </c>
     </row>
     <row r="14">
@@ -1861,22 +1861,22 @@
         <v>81</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.538996500733657</v>
+        <v>-0.538996500733645</v>
       </c>
       <c r="C14" t="n">
-        <v>0.885285093087315</v>
+        <v>0.88528509308731</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.608839463063789</v>
+        <v>-0.608839463063779</v>
       </c>
       <c r="E14" t="n">
-        <v>0.542630853315977</v>
+        <v>0.542630853315983</v>
       </c>
       <c r="F14" t="n">
-        <v>0.583333333332767</v>
+        <v>0.583333333332774</v>
       </c>
       <c r="G14" t="n">
-        <v>0.102887059791463</v>
+        <v>0.102887059791465</v>
       </c>
       <c r="H14" t="n">
         <v>3.30729421626792</v>
@@ -1887,25 +1887,25 @@
         <v>82</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.875468737353696</v>
+        <v>-0.875468737353694</v>
       </c>
       <c r="C15" t="n">
-        <v>0.855374977210193</v>
+        <v>0.855374977210197</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.02349117133288</v>
+        <v>-1.02349117133287</v>
       </c>
       <c r="E15" t="n">
-        <v>0.306075672092306</v>
+        <v>0.306075672092309</v>
       </c>
       <c r="F15" t="n">
         <v>0.416666666666752</v>
       </c>
       <c r="G15" t="n">
-        <v>0.077927771636308</v>
+        <v>0.0779277716363075</v>
       </c>
       <c r="H15" t="n">
-        <v>2.22784647200528</v>
+        <v>2.2278464720053</v>
       </c>
     </row>
     <row r="16">
@@ -1913,25 +1913,25 @@
         <v>83</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.391671785978329</v>
+        <v>-0.391671785978315</v>
       </c>
       <c r="C16" t="n">
-        <v>0.822031190500935</v>
+        <v>0.822031190500929</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.476468278216608</v>
+        <v>-0.476468278216595</v>
       </c>
       <c r="E16" t="n">
-        <v>0.63374080155733</v>
+        <v>0.63374080155734</v>
       </c>
       <c r="F16" t="n">
-        <v>0.675925925924236</v>
+        <v>0.675925925924245</v>
       </c>
       <c r="G16" t="n">
-        <v>0.134953728178764</v>
+        <v>0.134953728178767</v>
       </c>
       <c r="H16" t="n">
-        <v>3.38542597897958</v>
+        <v>3.38542597897959</v>
       </c>
     </row>
     <row r="17">
@@ -1939,25 +1939,25 @@
         <v>84</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.196710294248064</v>
+        <v>-0.196710294248052</v>
       </c>
       <c r="C17" t="n">
-        <v>0.900741255052832</v>
+        <v>0.900741255052828</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.218387126319119</v>
+        <v>-0.218387126319106</v>
       </c>
       <c r="E17" t="n">
-        <v>0.827127495188492</v>
+        <v>0.827127495188502</v>
       </c>
       <c r="F17" t="n">
-        <v>0.82142857142692</v>
+        <v>0.82142857142693</v>
       </c>
       <c r="G17" t="n">
-        <v>0.140558611493651</v>
+        <v>0.140558611493654</v>
       </c>
       <c r="H17" t="n">
-        <v>4.80045221552965</v>
+        <v>4.80045221552968</v>
       </c>
     </row>
     <row r="18">
@@ -1965,22 +1965,22 @@
         <v>85</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.513806251905356</v>
+        <v>-0.513806251905346</v>
       </c>
       <c r="C18" t="n">
-        <v>0.806423891570397</v>
+        <v>0.806423891570391</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.637141653758287</v>
+        <v>-0.637141653758279</v>
       </c>
       <c r="E18" t="n">
-        <v>0.524032578605876</v>
+        <v>0.524032578605882</v>
       </c>
       <c r="F18" t="n">
-        <v>0.598214285713551</v>
+        <v>0.598214285713557</v>
       </c>
       <c r="G18" t="n">
-        <v>0.123148044240777</v>
+        <v>0.12314804424078</v>
       </c>
       <c r="H18" t="n">
         <v>2.90593597192733</v>
@@ -2072,7 +2072,7 @@
         <v>0.631490619143657</v>
       </c>
       <c r="D3" t="n">
-        <v>0.752664466967638</v>
+        <v>0.752664466967639</v>
       </c>
     </row>
     <row r="4">
@@ -2083,7 +2083,7 @@
         <v>0.727777777777262</v>
       </c>
       <c r="C4" t="n">
-        <v>0.658174146473558</v>
+        <v>0.658174146473559</v>
       </c>
       <c r="D4" t="n">
         <v>0.787778413451973</v>
@@ -2094,13 +2094,13 @@
         <v>45</v>
       </c>
       <c r="B5" t="n">
-        <v>0.709999999999655</v>
+        <v>0.709999999999656</v>
       </c>
       <c r="C5" t="n">
         <v>0.66360832407841</v>
       </c>
       <c r="D5" t="n">
-        <v>0.752381112753435</v>
+        <v>0.752381112753436</v>
       </c>
     </row>
     <row r="7">
@@ -2142,13 +2142,13 @@
         <v>0.825745302000503</v>
       </c>
       <c r="C9" t="n">
-        <v>0.14649676506263</v>
+        <v>0.146496765062631</v>
       </c>
       <c r="D9" t="n">
         <v>5.63661116781302</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0000000173429095614061</v>
+        <v>0.0000000173429095614068</v>
       </c>
       <c r="F9" t="n">
         <v>2.28358208955003</v>
@@ -2165,25 +2165,25 @@
         <v>90</v>
       </c>
       <c r="B10" t="n">
-        <v>0.157631723087418</v>
+        <v>0.157631723087421</v>
       </c>
       <c r="C10" t="n">
         <v>0.222492719085246</v>
       </c>
       <c r="D10" t="n">
-        <v>0.70848036616885</v>
+        <v>0.70848036616886</v>
       </c>
       <c r="E10" t="n">
-        <v>0.478647000569834</v>
+        <v>0.478647000569828</v>
       </c>
       <c r="F10" t="n">
         <v>1.17073496064901</v>
       </c>
       <c r="G10" t="n">
-        <v>0.756959147631158</v>
+        <v>0.756959147631159</v>
       </c>
       <c r="H10" t="n">
-        <v>1.81069262770003</v>
+        <v>1.81069262770004</v>
       </c>
     </row>
     <row r="12">
@@ -2210,13 +2210,13 @@
         <v>91</v>
       </c>
       <c r="B14" t="n">
-        <v>0.503662196646985</v>
+        <v>0.503662196647099</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.477895389392937</v>
+        <v>0.477895389392887</v>
       </c>
     </row>
   </sheetData>
@@ -2266,13 +2266,13 @@
         <v>93</v>
       </c>
       <c r="B3" t="n">
-        <v>0.651741293532322</v>
+        <v>0.651741293532323</v>
       </c>
       <c r="C3" t="n">
         <v>0.583346433876446</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7144055551573</v>
+        <v>0.714405555157301</v>
       </c>
     </row>
     <row r="4">
@@ -2286,7 +2286,7 @@
         <v>0.666083343066893</v>
       </c>
       <c r="D4" t="n">
-        <v>0.805236666000544</v>
+        <v>0.805236666000545</v>
       </c>
     </row>
     <row r="5">
@@ -2294,7 +2294,7 @@
         <v>95</v>
       </c>
       <c r="B5" t="n">
-        <v>0.854166666666666</v>
+        <v>0.854166666666665</v>
       </c>
       <c r="C5" t="n">
         <v>0.724344905378273</v>
@@ -2308,13 +2308,13 @@
         <v>45</v>
       </c>
       <c r="B6" t="n">
-        <v>0.709999999999655</v>
+        <v>0.709999999999656</v>
       </c>
       <c r="C6" t="n">
         <v>0.66360832407841</v>
       </c>
       <c r="D6" t="n">
-        <v>0.752381112753435</v>
+        <v>0.752381112753436</v>
       </c>
     </row>
     <row r="8">
@@ -2353,16 +2353,16 @@
         <v>54</v>
       </c>
       <c r="B10" t="n">
-        <v>0.62670208115172</v>
+        <v>0.626702081151724</v>
       </c>
       <c r="C10" t="n">
-        <v>0.14805167196943</v>
+        <v>0.148051671969431</v>
       </c>
       <c r="D10" t="n">
-        <v>4.23299563466681</v>
+        <v>4.23299563466682</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0000230598982768473</v>
+        <v>0.0000230598982768457</v>
       </c>
       <c r="F10" t="n">
         <v>1.87142857142844</v>
@@ -2371,7 +2371,7 @@
         <v>1.40007546150094</v>
       </c>
       <c r="H10" t="n">
-        <v>2.50146866669896</v>
+        <v>2.50146866669897</v>
       </c>
     </row>
     <row r="11">
@@ -2379,25 +2379,25 @@
         <v>96</v>
       </c>
       <c r="B11" t="n">
-        <v>0.42823514401072</v>
+        <v>0.428235144010718</v>
       </c>
       <c r="C11" t="n">
-        <v>0.237673801104186</v>
+        <v>0.237673801104187</v>
       </c>
       <c r="D11" t="n">
-        <v>1.80177681352014</v>
+        <v>1.80177681352013</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0715805271294189</v>
+        <v>0.0715805271294207</v>
       </c>
       <c r="F11" t="n">
         <v>1.53454687805382</v>
       </c>
       <c r="G11" t="n">
-        <v>0.963101044186939</v>
+        <v>0.963101044186936</v>
       </c>
       <c r="H11" t="n">
-        <v>2.44505406276734</v>
+        <v>2.44505406276733</v>
       </c>
     </row>
     <row r="12">
@@ -2405,25 +2405,25 @@
         <v>97</v>
       </c>
       <c r="B12" t="n">
-        <v>1.14095983649727</v>
+        <v>1.14095983649726</v>
       </c>
       <c r="C12" t="n">
-        <v>0.434932941491295</v>
+        <v>0.434932941491292</v>
       </c>
       <c r="D12" t="n">
         <v>2.62330057729164</v>
       </c>
       <c r="E12" t="n">
-        <v>0.00870824083831561</v>
+        <v>0.00870824083831568</v>
       </c>
       <c r="F12" t="n">
-        <v>3.12977099236661</v>
+        <v>3.12977099236659</v>
       </c>
       <c r="G12" t="n">
-        <v>1.33443360443407</v>
+        <v>1.33443360443406</v>
       </c>
       <c r="H12" t="n">
-        <v>7.34054240848778</v>
+        <v>7.34054240848769</v>
       </c>
     </row>
     <row r="14">
@@ -2450,13 +2450,13 @@
         <v>98</v>
       </c>
       <c r="B16" t="n">
-        <v>9.48720495948407</v>
+        <v>9.48720495948413</v>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>0.00870722202605101</v>
+        <v>0.00870722202605076</v>
       </c>
     </row>
   </sheetData>
@@ -2532,7 +2532,7 @@
         <v>0.694094586811876</v>
       </c>
       <c r="D4" t="n">
-        <v>0.605415989041319</v>
+        <v>0.605415989041318</v>
       </c>
       <c r="E4" t="n">
         <v>0.770401709258948</v>
@@ -2546,13 +2546,13 @@
         <v>60</v>
       </c>
       <c r="C5" t="n">
-        <v>0.822999832230719</v>
+        <v>0.82299983223072</v>
       </c>
       <c r="D5" t="n">
-        <v>0.672779824704765</v>
+        <v>0.672779824704766</v>
       </c>
       <c r="E5" t="n">
-        <v>0.913158573265295</v>
+        <v>0.913158573265296</v>
       </c>
     </row>
     <row r="6">
@@ -2563,10 +2563,10 @@
         <v>61</v>
       </c>
       <c r="C6" t="n">
-        <v>0.742307673873539</v>
+        <v>0.742307673873538</v>
       </c>
       <c r="D6" t="n">
-        <v>0.655458661499955</v>
+        <v>0.655458661499954</v>
       </c>
       <c r="E6" t="n">
         <v>0.813493794736284</v>
@@ -2580,13 +2580,13 @@
         <v>61</v>
       </c>
       <c r="C7" t="n">
-        <v>0.82485308483733</v>
+        <v>0.824853084837329</v>
       </c>
       <c r="D7" t="n">
-        <v>0.740579229228728</v>
+        <v>0.740579229228727</v>
       </c>
       <c r="E7" t="n">
-        <v>0.885965707245667</v>
+        <v>0.885965707245666</v>
       </c>
     </row>
     <row r="8">
@@ -2614,13 +2614,13 @@
         <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>0.709999999999655</v>
+        <v>0.709999999999656</v>
       </c>
       <c r="D9" t="n">
         <v>0.66360832407841</v>
       </c>
       <c r="E9" t="n">
-        <v>0.752381112753435</v>
+        <v>0.752381112753436</v>
       </c>
     </row>
     <row r="11">
@@ -2665,16 +2665,16 @@
         <v>0.175752441137518</v>
       </c>
       <c r="D13" t="n">
-        <v>1.86483677262341</v>
+        <v>1.8648367726234</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0622042871687992</v>
+        <v>0.0622042871688006</v>
       </c>
       <c r="F13" t="n">
         <v>1.38784143425942</v>
       </c>
       <c r="G13" t="n">
-        <v>0.983420144458427</v>
+        <v>0.983420144458425</v>
       </c>
       <c r="H13" t="n">
         <v>1.95857676650295</v>
@@ -2685,16 +2685,16 @@
         <v>96</v>
       </c>
       <c r="B14" t="n">
-        <v>0.491582681403881</v>
+        <v>0.491582681403878</v>
       </c>
       <c r="C14" t="n">
         <v>0.241706234817773</v>
       </c>
       <c r="D14" t="n">
-        <v>2.03380223838452</v>
+        <v>2.03380223838451</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0419715387696621</v>
+        <v>0.0419715387696631</v>
       </c>
       <c r="F14" t="n">
         <v>1.63490170193939</v>
@@ -2714,22 +2714,22 @@
         <v>1.20905570129217</v>
       </c>
       <c r="C15" t="n">
-        <v>0.439133873113297</v>
+        <v>0.439133873113298</v>
       </c>
       <c r="D15" t="n">
-        <v>2.75327360360613</v>
+        <v>2.75327360360614</v>
       </c>
       <c r="E15" t="n">
-        <v>0.00590025632556846</v>
+        <v>0.00590025632556826</v>
       </c>
       <c r="F15" t="n">
-        <v>3.35031945600558</v>
+        <v>3.35031945600561</v>
       </c>
       <c r="G15" t="n">
-        <v>1.41675511381217</v>
+        <v>1.41675511381218</v>
       </c>
       <c r="H15" t="n">
-        <v>7.92278097171397</v>
+        <v>7.92278097171403</v>
       </c>
     </row>
     <row r="16">
@@ -2737,25 +2737,25 @@
         <v>62</v>
       </c>
       <c r="B16" t="n">
-        <v>0.730247858033252</v>
+        <v>0.730247858033248</v>
       </c>
       <c r="C16" t="n">
         <v>0.240468313332661</v>
       </c>
       <c r="D16" t="n">
-        <v>3.03677373502028</v>
+        <v>3.03677373502027</v>
       </c>
       <c r="E16" t="n">
-        <v>0.00239124878511212</v>
+        <v>0.00239124878511222</v>
       </c>
       <c r="F16" t="n">
-        <v>2.07559499681749</v>
+        <v>2.07559499681748</v>
       </c>
       <c r="G16" t="n">
         <v>1.29555428706739</v>
       </c>
       <c r="H16" t="n">
-        <v>3.32529067582769</v>
+        <v>3.32529067582768</v>
       </c>
     </row>
     <row r="18">
@@ -2788,7 +2788,7 @@
         <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>0.00449764997079779</v>
+        <v>0.00449764997079792</v>
       </c>
     </row>
     <row r="21">
@@ -2796,13 +2796,13 @@
         <v>100</v>
       </c>
       <c r="B21" t="n">
-        <v>9.6599333261409</v>
+        <v>9.65993332614084</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.00188330455571076</v>
+        <v>0.00188330455571081</v>
       </c>
     </row>
   </sheetData>
